--- a/Empleos.xlsx
+++ b/Empleos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\54292\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3EA9368-CEFC-4E6B-803E-00C7F46AE7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B8C1CF-A655-4BA3-874E-D1CBB641480B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -291,6 +291,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -358,6 +359,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1033,10 +1035,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1052,22 +1054,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF007BE0"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF007BE0"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF007BE0"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF007BE0"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1092,13 +1078,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF007BE0"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF007BE0"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF007BE0"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF007BE0"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Carga Seguimiento Reclutamiento-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1113,6 +1115,49 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2266950" cy="333375"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="image1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71AB2D14-18D2-4164-AB49-CD181D7EC42B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2266950" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -29661,6 +29706,7 @@
   </dataValidations>
   <pageMargins left="0.24719101123595505" right="0.27918472971777408" top="0.21629213483146068" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29697,10 +29743,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="33.75" customHeight="1">
-      <c r="A1" s="99"/>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
+      <c r="A1" s="98"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
